--- a/data/template/Template_Insert_Ring.xlsx
+++ b/data/template/Template_Insert_Ring.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JACOBS\PROJECT\TASK\NOVEMBER\Week 4\Insert Algorithm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JACOBS\SERVICE\API\data\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABE4A58-D418-43B8-A858-1033C9C6B7BC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DCB7BB-805C-4A41-92F5-67A91426B352}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="145">
-  <si>
-    <t>Ring ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="112">
   <si>
     <t>Site ID</t>
   </si>
@@ -46,9 +43,6 @@
     <t>Program</t>
   </si>
   <si>
-    <t>TBG-PBR-MOCNPhase1-DF046</t>
-  </si>
-  <si>
     <t>04PBR0143</t>
   </si>
   <si>
@@ -76,9 +70,6 @@
     <t>IN_PASAR_KODIM_IJ</t>
   </si>
   <si>
-    <t>TBG-PAD-MOCNPhase1-DF170</t>
-  </si>
-  <si>
     <t>03PDN0080</t>
   </si>
   <si>
@@ -97,9 +88,6 @@
     <t>PASAR_ULAK_KARANG_TB</t>
   </si>
   <si>
-    <t>TBG-PAT-MOCNPhase1-DF042</t>
-  </si>
-  <si>
     <t>14PAT0079</t>
   </si>
   <si>
@@ -109,9 +97,6 @@
     <t>CJRO</t>
   </si>
   <si>
-    <t>TBG-TAG-MOCNPhase2-DF164</t>
-  </si>
-  <si>
     <t>16TAG0027</t>
   </si>
   <si>
@@ -121,9 +106,6 @@
     <t>EJRO</t>
   </si>
   <si>
-    <t>TBG-PAT-Phase4a-DF054</t>
-  </si>
-  <si>
     <t>14PAT0108</t>
   </si>
   <si>
@@ -136,9 +118,6 @@
     <t>MARGOYOSO_MARGOYOSO_PL</t>
   </si>
   <si>
-    <t>TBG-SDA-Phase4a-DF017</t>
-  </si>
-  <si>
     <t>16SDA0156</t>
   </si>
   <si>
@@ -151,36 +130,24 @@
     <t>PERMATA_SIDOARJO_REGENCY_BA</t>
   </si>
   <si>
-    <t>TBG-PBR-Phase4a-DF010</t>
-  </si>
-  <si>
     <t>04PBR0122</t>
   </si>
   <si>
     <t>AIR_HITAM_PBR2_PL</t>
   </si>
   <si>
-    <t>TBG-BKG-Phase4a-DF204</t>
-  </si>
-  <si>
     <t>04PBR0012</t>
   </si>
   <si>
     <t>AIR_HITAM_PBR1_MT</t>
   </si>
   <si>
-    <t>TBG-KBM-MOCNPhase1-DF100</t>
-  </si>
-  <si>
     <t>14KBM0074</t>
   </si>
   <si>
     <t>I2_RITAKEBUMEN_DH</t>
   </si>
   <si>
-    <t>TBG-TBT-MOCNPhase1-DF125</t>
-  </si>
-  <si>
     <t>02TBT0033</t>
   </si>
   <si>
@@ -193,18 +160,12 @@
     <t>SATRIA_TBT_PL</t>
   </si>
   <si>
-    <t>TBG-MDN-MOCNPhase1-DF088</t>
-  </si>
-  <si>
     <t>02MDN0406</t>
   </si>
   <si>
     <t>IN_MEDAN_MALL_MC</t>
   </si>
   <si>
-    <t>TBG-MDN-Phase4a-DF002</t>
-  </si>
-  <si>
     <t>02MDN0015</t>
   </si>
   <si>
@@ -223,18 +184,12 @@
     <t>ASOKAMEDANSELAYANG_MT</t>
   </si>
   <si>
-    <t>TBG-PAD-Phase4a-DF002</t>
-  </si>
-  <si>
     <t>03PDN0147</t>
   </si>
   <si>
     <t>AIE_PACAH_MT</t>
   </si>
   <si>
-    <t>TBG-BKN-Phase4a-DF004</t>
-  </si>
-  <si>
     <t>04PBR0027</t>
   </si>
   <si>
@@ -247,18 +202,12 @@
     <t>CEMARA_KIPAS_GT</t>
   </si>
   <si>
-    <t>TBG-TJG-Phase4a-DF191</t>
-  </si>
-  <si>
     <t>05TJG0028</t>
   </si>
   <si>
     <t>SULTAN_MAHMUD_MT</t>
   </si>
   <si>
-    <t>TBG-PAD-Phase4a-DF196</t>
-  </si>
-  <si>
     <t>03PDN0192</t>
   </si>
   <si>
@@ -271,36 +220,24 @@
     <t>BANDESANDURING_PL</t>
   </si>
   <si>
-    <t>TBG-PAD-Phase4a-DF009</t>
-  </si>
-  <si>
     <t>03PDN0233</t>
   </si>
   <si>
     <t>PADANG_BESI_PL</t>
   </si>
   <si>
-    <t>TBG-TBN-Phase4a-DF004</t>
-  </si>
-  <si>
     <t>16TBN0178</t>
   </si>
   <si>
     <t>DESA_RAWASAN_PL</t>
   </si>
   <si>
-    <t>TBG-CJRO-Phase4a-DF010</t>
-  </si>
-  <si>
     <t>15WOS0053</t>
   </si>
   <si>
     <t>TEPUS_EP</t>
   </si>
   <si>
-    <t>TBG-KLA-MOCNPhase1-DF077</t>
-  </si>
-  <si>
     <t>09TJK0199</t>
   </si>
   <si>
@@ -322,9 +259,6 @@
     <t>GUNUNG_SULA_PL</t>
   </si>
   <si>
-    <t>TBG-TNR-Tomahawk-DF055</t>
-  </si>
-  <si>
     <t>22TNR0056</t>
   </si>
   <si>
@@ -334,9 +268,6 @@
     <t>KRO</t>
   </si>
   <si>
-    <t>TBG-SMR-Q2Expansion-DF011</t>
-  </si>
-  <si>
     <t>22SMR0050</t>
   </si>
   <si>
@@ -349,72 +280,48 @@
     <t>GRAND_VICTORIA_EP</t>
   </si>
   <si>
-    <t>TBG-SMR-MOCNPhase2-DF030</t>
-  </si>
-  <si>
     <t>22SMR0227</t>
   </si>
   <si>
     <t>BANTUAS_PALARAN_PL</t>
   </si>
   <si>
-    <t>TBG-KTP-Phase4a-DF095</t>
-  </si>
-  <si>
     <t>20KTP0002</t>
   </si>
   <si>
     <t>SKBANGUN_DALAM_TB</t>
   </si>
   <si>
-    <t>TBG-AMT-Phase4a-DF129</t>
-  </si>
-  <si>
     <t>23AMT0029</t>
   </si>
   <si>
     <t>KEBUN_SARI_ST</t>
   </si>
   <si>
-    <t>TBG-NGB-Q3AOP2023-DF001</t>
-  </si>
-  <si>
     <t>21NIK0047</t>
   </si>
   <si>
     <t>BATU_BATANGGUI_PL</t>
   </si>
   <si>
-    <t>TBG-NBA-Q2Expansion-DF021</t>
-  </si>
-  <si>
     <t>20NBA0002</t>
   </si>
   <si>
     <t>KAYU_TANAM_NBA2_PL</t>
   </si>
   <si>
-    <t>TBG-NBA-Q2Expansion-DF022</t>
-  </si>
-  <si>
     <t>20NBA0021</t>
   </si>
   <si>
     <t>AUR_SAMPUK_MT</t>
   </si>
   <si>
-    <t>TBG-PTS-Q2CapExpansion2024-DF067</t>
-  </si>
-  <si>
     <t>20PTS0067</t>
   </si>
   <si>
     <t>PANGSUMA_AIRPORT_PL</t>
   </si>
   <si>
-    <t>TBG-BLS-Q2Expansion-DF016</t>
-  </si>
-  <si>
     <t>04BLS0025</t>
   </si>
   <si>
@@ -427,9 +334,6 @@
     <t>KANGEN1_MT</t>
   </si>
   <si>
-    <t>TBG-TAK-Phase4a-DF002</t>
-  </si>
-  <si>
     <t>04TAK0016</t>
   </si>
   <si>
@@ -440,9 +344,6 @@
   </si>
   <si>
     <t>LANGSAT_HULU_MT</t>
-  </si>
-  <si>
-    <t>TBG-KIS-Phase4a-DF163</t>
   </si>
   <si>
     <t>02KIS0085</t>
@@ -1295,10 +1196,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1320,1282 +1221,1132 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
+      <c r="C2">
+        <v>101.42328999999999</v>
       </c>
       <c r="D2">
-        <v>101.42328999999999</v>
-      </c>
-      <c r="E2">
         <v>0.54040999999999995</v>
       </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3">
+        <v>101.42773</v>
+      </c>
+      <c r="D3">
+        <v>0.53978999999999999</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="D3">
-        <v>101.42773</v>
-      </c>
-      <c r="E3">
-        <v>0.53978999999999999</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4">
+        <v>101.44167</v>
+      </c>
+      <c r="D4">
+        <v>0.53056000000000003</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="D4">
-        <v>101.44167</v>
-      </c>
-      <c r="E4">
-        <v>0.53056000000000003</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
+      <c r="C5">
+        <v>100.363</v>
       </c>
       <c r="D5">
-        <v>100.363</v>
-      </c>
-      <c r="E5">
         <v>-0.92710000000000004</v>
       </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>100.35799</v>
+      </c>
+      <c r="D6">
+        <v>-0.91257999999999995</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7">
+        <v>100.35</v>
+      </c>
+      <c r="D7">
+        <v>-0.91364999999999996</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="D6">
-        <v>100.35799</v>
-      </c>
-      <c r="E6">
-        <v>-0.91257999999999995</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8">
+        <v>111.04684</v>
+      </c>
+      <c r="D8">
+        <v>-6.7325299999999997</v>
+      </c>
+      <c r="E8" t="s">
         <v>24</v>
       </c>
-      <c r="D7">
-        <v>100.35</v>
-      </c>
-      <c r="E7">
-        <v>-0.91364999999999996</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>25</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9">
+        <v>111.84614000000001</v>
+      </c>
+      <c r="D9">
+        <v>-8.1246899999999993</v>
+      </c>
+      <c r="E9" t="s">
         <v>27</v>
       </c>
-      <c r="D8">
-        <v>111.04684</v>
-      </c>
-      <c r="E8">
-        <v>-6.7325299999999997</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="G8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B10" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C10">
+        <v>111.06310999999999</v>
+      </c>
+      <c r="D10">
+        <v>-6.6002400000000003</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="D9">
-        <v>111.84614000000001</v>
-      </c>
-      <c r="E9">
-        <v>-8.1246899999999993</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="C11">
+        <v>111.06431000000001</v>
+      </c>
+      <c r="D11">
+        <v>-6.5924199999999997</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>32</v>
       </c>
-      <c r="G9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B12" t="s">
         <v>33</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C12">
+        <v>112.67862</v>
+      </c>
+      <c r="D12">
+        <v>-7.4958600000000004</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="D10">
-        <v>111.06310999999999</v>
-      </c>
-      <c r="E10">
-        <v>-6.6002400000000003</v>
-      </c>
-      <c r="F10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C13">
+        <v>112.70261000000001</v>
+      </c>
+      <c r="D13">
+        <v>-7.5037599999999998</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>36</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="D11">
-        <v>111.06431000000001</v>
-      </c>
-      <c r="E11">
-        <v>-6.5924199999999997</v>
-      </c>
-      <c r="F11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C14">
+        <v>101.41916999999999</v>
+      </c>
+      <c r="D14">
+        <v>0.53244999999999998</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>38</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B15" t="s">
         <v>39</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C15">
+        <v>101.36835000000001</v>
+      </c>
+      <c r="D15">
+        <v>0.49974000000000002</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>40</v>
       </c>
-      <c r="D12">
-        <v>112.67862</v>
-      </c>
-      <c r="E12">
-        <v>-7.4958600000000004</v>
-      </c>
-      <c r="F12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="B16" t="s">
         <v>41</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C16">
+        <v>109.65649999999999</v>
+      </c>
+      <c r="D16">
+        <v>-7.6699200000000003</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>42</v>
       </c>
-      <c r="D13">
-        <v>112.70261000000001</v>
-      </c>
-      <c r="E13">
-        <v>-7.5037599999999998</v>
-      </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B17" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C17">
+        <v>99.166569999999993</v>
+      </c>
+      <c r="D17">
+        <v>3.3250099999999998</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>44</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B18" t="s">
         <v>45</v>
       </c>
-      <c r="D14">
-        <v>101.41916999999999</v>
-      </c>
-      <c r="E14">
-        <v>0.53244999999999998</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="C18">
+        <v>99.170400000000001</v>
+      </c>
+      <c r="D18">
+        <v>3.3297599999999998</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>46</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B19" t="s">
         <v>47</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C19">
+        <v>98.686920000000001</v>
+      </c>
+      <c r="D19">
+        <v>3.5880800000000002</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>48</v>
       </c>
-      <c r="D15">
-        <v>101.36835000000001</v>
-      </c>
-      <c r="E15">
-        <v>0.49974000000000002</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B20" t="s">
         <v>49</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C20">
+        <v>98.609759999999994</v>
+      </c>
+      <c r="D20">
+        <v>3.5494500000000002</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>50</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B21" t="s">
         <v>51</v>
       </c>
-      <c r="D16">
-        <v>109.65649999999999</v>
-      </c>
-      <c r="E16">
-        <v>-7.6699200000000003</v>
-      </c>
-      <c r="F16" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="C21">
+        <v>98.617609999999999</v>
+      </c>
+      <c r="D21">
+        <v>3.5617700000000001</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>52</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B22" t="s">
         <v>53</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C22">
+        <v>98.620999999999995</v>
+      </c>
+      <c r="D22">
+        <v>3.5648300000000002</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>54</v>
       </c>
-      <c r="D17">
-        <v>99.166569999999993</v>
-      </c>
-      <c r="E17">
-        <v>3.3250099999999998</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="B23" t="s">
         <v>55</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C23">
+        <v>100.38639999999999</v>
+      </c>
+      <c r="D23">
+        <v>-0.89912999999999998</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>56</v>
       </c>
-      <c r="D18">
-        <v>99.170400000000001</v>
-      </c>
-      <c r="E18">
-        <v>3.3297599999999998</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B24" t="s">
         <v>57</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C24">
+        <v>101.37954000000001</v>
+      </c>
+      <c r="D24">
+        <v>0.46812999999999999</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>58</v>
       </c>
-      <c r="C19" t="s">
+      <c r="B25" t="s">
         <v>59</v>
       </c>
-      <c r="D19">
-        <v>98.686920000000001</v>
-      </c>
-      <c r="E19">
-        <v>3.5880800000000002</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="C25">
+        <v>101.41200000000001</v>
+      </c>
+      <c r="D25">
+        <v>0.47427999999999998</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>60</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B26" t="s">
         <v>61</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C26">
+        <v>104.46536</v>
+      </c>
+      <c r="D26">
+        <v>0.92771999999999999</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>62</v>
       </c>
-      <c r="D20">
-        <v>98.609759999999994</v>
-      </c>
-      <c r="E20">
-        <v>3.5494500000000002</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" t="s">
-        <v>12</v>
-      </c>
-      <c r="H20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="B27" t="s">
         <v>63</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C27">
+        <v>100.405</v>
+      </c>
+      <c r="D27">
+        <v>-0.88815</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>64</v>
       </c>
-      <c r="D21">
-        <v>98.617609999999999</v>
-      </c>
-      <c r="E21">
-        <v>3.5617700000000001</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="B28" t="s">
         <v>65</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C28">
+        <v>100.37808</v>
+      </c>
+      <c r="D28">
+        <v>-0.93301999999999996</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>66</v>
       </c>
-      <c r="D22">
-        <v>98.620999999999995</v>
-      </c>
-      <c r="E22">
-        <v>3.5648300000000002</v>
-      </c>
-      <c r="F22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B29" t="s">
         <v>67</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C29">
+        <v>100.45061</v>
+      </c>
+      <c r="D29">
+        <v>-0.95757999999999999</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>68</v>
       </c>
-      <c r="C23" t="s">
+      <c r="B30" t="s">
         <v>69</v>
       </c>
-      <c r="D23">
-        <v>100.38639999999999</v>
-      </c>
-      <c r="E23">
-        <v>-0.89912999999999998</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" t="s">
-        <v>12</v>
-      </c>
-      <c r="H23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="C30">
+        <v>111.9761111</v>
+      </c>
+      <c r="D30">
+        <v>-6.7945277800000001</v>
+      </c>
+      <c r="E30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>70</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B31" t="s">
         <v>71</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C31">
+        <v>110.627</v>
+      </c>
+      <c r="D31">
+        <v>-8.0922400000000003</v>
+      </c>
+      <c r="E31" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>72</v>
       </c>
-      <c r="D24">
-        <v>101.37954000000001</v>
-      </c>
-      <c r="E24">
-        <v>0.46812999999999999</v>
-      </c>
-      <c r="F24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="B32" t="s">
         <v>73</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C32">
+        <v>105.28211</v>
+      </c>
+      <c r="D32">
+        <v>-5.3830600000000004</v>
+      </c>
+      <c r="E32" t="s">
         <v>74</v>
       </c>
-      <c r="D25">
-        <v>101.41200000000001</v>
-      </c>
-      <c r="E25">
-        <v>0.47427999999999998</v>
-      </c>
-      <c r="F25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" t="s">
-        <v>12</v>
-      </c>
-      <c r="H25" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="F32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>75</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B33" t="s">
         <v>76</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C33">
+        <v>105.27692</v>
+      </c>
+      <c r="D33">
+        <v>-5.3914499999999999</v>
+      </c>
+      <c r="E33" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>77</v>
       </c>
-      <c r="D26">
-        <v>104.46536</v>
-      </c>
-      <c r="E26">
-        <v>0.92771999999999999</v>
-      </c>
-      <c r="F26" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B34" t="s">
         <v>78</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C34">
+        <v>105.27185</v>
+      </c>
+      <c r="D34">
+        <v>-5.3888999999999996</v>
+      </c>
+      <c r="E34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>79</v>
       </c>
-      <c r="C27" t="s">
+      <c r="B35" t="s">
         <v>80</v>
       </c>
-      <c r="D27">
-        <v>100.405</v>
-      </c>
-      <c r="E27">
-        <v>-0.88815</v>
-      </c>
-      <c r="F27" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" t="s">
-        <v>12</v>
-      </c>
-      <c r="H27" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="C35">
+        <v>117.47207</v>
+      </c>
+      <c r="D35">
+        <v>2.1488299999999998</v>
+      </c>
+      <c r="E35" t="s">
         <v>81</v>
       </c>
-      <c r="C28" t="s">
+      <c r="F35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>82</v>
       </c>
-      <c r="D28">
-        <v>100.37808</v>
-      </c>
-      <c r="E28">
-        <v>-0.93301999999999996</v>
-      </c>
-      <c r="F28" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B36" t="s">
         <v>83</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C36">
+        <v>117.12284</v>
+      </c>
+      <c r="D36">
+        <v>-0.50209000000000004</v>
+      </c>
+      <c r="E36" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>84</v>
       </c>
-      <c r="C29" t="s">
+      <c r="B37" t="s">
         <v>85</v>
       </c>
-      <c r="D29">
-        <v>100.45061</v>
-      </c>
-      <c r="E29">
-        <v>-0.95757999999999999</v>
-      </c>
-      <c r="F29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" t="s">
-        <v>12</v>
-      </c>
-      <c r="H29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="C37">
+        <v>117.14816999999999</v>
+      </c>
+      <c r="D37">
+        <v>-0.47642000000000001</v>
+      </c>
+      <c r="E37" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>86</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B38" t="s">
         <v>87</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C38">
+        <v>11721049</v>
+      </c>
+      <c r="D38">
+        <v>-0.64832999999999996</v>
+      </c>
+      <c r="E38" t="s">
+        <v>81</v>
+      </c>
+      <c r="F38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>88</v>
       </c>
-      <c r="D30">
-        <v>111.9761111</v>
-      </c>
-      <c r="E30">
-        <v>-6.7945277800000001</v>
-      </c>
-      <c r="F30" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" t="s">
-        <v>12</v>
-      </c>
-      <c r="H30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B39" t="s">
         <v>89</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C39">
+        <v>109.95220999999999</v>
+      </c>
+      <c r="D39">
+        <v>-1.7906299999999999</v>
+      </c>
+      <c r="E39" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>90</v>
       </c>
-      <c r="C31" t="s">
+      <c r="B40" t="s">
         <v>91</v>
       </c>
-      <c r="D31">
-        <v>110.627</v>
-      </c>
-      <c r="E31">
-        <v>-8.0922400000000003</v>
-      </c>
-      <c r="F31" t="s">
-        <v>28</v>
-      </c>
-      <c r="G31" t="s">
-        <v>12</v>
-      </c>
-      <c r="H31" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="C40">
+        <v>115.246</v>
+      </c>
+      <c r="D40">
+        <v>-2.4285399999999999</v>
+      </c>
+      <c r="E40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>92</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B41" t="s">
         <v>93</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C41">
+        <v>111.43434000000001</v>
+      </c>
+      <c r="D41">
+        <v>-2.1887400000000001</v>
+      </c>
+      <c r="E41" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>94</v>
       </c>
-      <c r="D32">
-        <v>105.28211</v>
-      </c>
-      <c r="E32">
-        <v>-5.3830600000000004</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="B42" t="s">
         <v>95</v>
       </c>
-      <c r="G32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>92</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="C42">
+        <v>109.28449000000001</v>
+      </c>
+      <c r="D42">
+        <v>0.34316999999999998</v>
+      </c>
+      <c r="E42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>96</v>
       </c>
-      <c r="C33" t="s">
+      <c r="B43" t="s">
         <v>97</v>
       </c>
-      <c r="D33">
-        <v>105.27692</v>
-      </c>
-      <c r="E33">
-        <v>-5.3914499999999999</v>
-      </c>
-      <c r="F33" t="s">
-        <v>95</v>
-      </c>
-      <c r="G33" t="s">
-        <v>12</v>
-      </c>
-      <c r="H33" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>92</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="C43">
+        <v>109.64293000000001</v>
+      </c>
+      <c r="D43">
+        <v>0.32357999999999998</v>
+      </c>
+      <c r="E43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>98</v>
       </c>
-      <c r="C34" t="s">
+      <c r="B44" t="s">
         <v>99</v>
       </c>
-      <c r="D34">
-        <v>105.27185</v>
-      </c>
-      <c r="E34">
-        <v>-5.3888999999999996</v>
-      </c>
-      <c r="F34" t="s">
-        <v>95</v>
-      </c>
-      <c r="G34" t="s">
-        <v>12</v>
-      </c>
-      <c r="H34" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="C44">
+        <v>112.92764</v>
+      </c>
+      <c r="D44">
+        <v>0.83287</v>
+      </c>
+      <c r="E44" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>100</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B45" t="s">
         <v>101</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C45">
+        <v>101.17953</v>
+      </c>
+      <c r="D45">
+        <v>1.26522</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>102</v>
       </c>
-      <c r="D35">
-        <v>117.47207</v>
-      </c>
-      <c r="E35">
-        <v>2.1488299999999998</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="B46" t="s">
         <v>103</v>
       </c>
-      <c r="G35" t="s">
-        <v>12</v>
-      </c>
-      <c r="H35" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="C46">
+        <v>101.18324</v>
+      </c>
+      <c r="D46">
+        <v>1.26054</v>
+      </c>
+      <c r="E46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>104</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B47" t="s">
         <v>105</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C47">
+        <v>101.51934</v>
+      </c>
+      <c r="D47">
+        <v>-0.38468000000000002</v>
+      </c>
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>106</v>
       </c>
-      <c r="D36">
-        <v>117.12284</v>
-      </c>
-      <c r="E36">
-        <v>-0.50209000000000004</v>
-      </c>
-      <c r="F36" t="s">
-        <v>103</v>
-      </c>
-      <c r="G36" t="s">
-        <v>12</v>
-      </c>
-      <c r="H36" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>104</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="B48" t="s">
         <v>107</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C48">
+        <v>101.55871999999999</v>
+      </c>
+      <c r="D48">
+        <v>-0.35905999999999999</v>
+      </c>
+      <c r="E48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>108</v>
       </c>
-      <c r="D37">
-        <v>117.14816999999999</v>
-      </c>
-      <c r="E37">
-        <v>-0.47642000000000001</v>
-      </c>
-      <c r="F37" t="s">
-        <v>103</v>
-      </c>
-      <c r="G37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H37" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="B49" t="s">
         <v>109</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C49">
+        <v>99.656499999999994</v>
+      </c>
+      <c r="D49">
+        <v>2.9799500000000001</v>
+      </c>
+      <c r="E49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>110</v>
       </c>
-      <c r="C38" t="s">
+      <c r="B50" t="s">
         <v>111</v>
       </c>
-      <c r="D38">
-        <v>11721049</v>
-      </c>
-      <c r="E38">
-        <v>-0.64832999999999996</v>
-      </c>
-      <c r="F38" t="s">
-        <v>103</v>
-      </c>
-      <c r="G38" t="s">
-        <v>12</v>
-      </c>
-      <c r="H38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>112</v>
-      </c>
-      <c r="B39" t="s">
-        <v>113</v>
-      </c>
-      <c r="C39" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39">
-        <v>109.95220999999999</v>
-      </c>
-      <c r="E39">
-        <v>-1.7906299999999999</v>
-      </c>
-      <c r="F39" t="s">
-        <v>103</v>
-      </c>
-      <c r="G39" t="s">
-        <v>12</v>
-      </c>
-      <c r="H39" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>115</v>
-      </c>
-      <c r="B40" t="s">
-        <v>116</v>
-      </c>
-      <c r="C40" t="s">
-        <v>117</v>
-      </c>
-      <c r="D40">
-        <v>115.246</v>
-      </c>
-      <c r="E40">
-        <v>-2.4285399999999999</v>
-      </c>
-      <c r="F40" t="s">
-        <v>103</v>
-      </c>
-      <c r="G40" t="s">
-        <v>12</v>
-      </c>
-      <c r="H40" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>118</v>
-      </c>
-      <c r="B41" t="s">
-        <v>119</v>
-      </c>
-      <c r="C41" t="s">
-        <v>120</v>
-      </c>
-      <c r="D41">
-        <v>111.43434000000001</v>
-      </c>
-      <c r="E41">
-        <v>-2.1887400000000001</v>
-      </c>
-      <c r="F41" t="s">
-        <v>103</v>
-      </c>
-      <c r="G41" t="s">
-        <v>12</v>
-      </c>
-      <c r="H41" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>121</v>
-      </c>
-      <c r="B42" t="s">
-        <v>122</v>
-      </c>
-      <c r="C42" t="s">
-        <v>123</v>
-      </c>
-      <c r="D42">
-        <v>109.28449000000001</v>
-      </c>
-      <c r="E42">
-        <v>0.34316999999999998</v>
-      </c>
-      <c r="F42" t="s">
-        <v>103</v>
-      </c>
-      <c r="G42" t="s">
-        <v>12</v>
-      </c>
-      <c r="H42" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>124</v>
-      </c>
-      <c r="B43" t="s">
-        <v>125</v>
-      </c>
-      <c r="C43" t="s">
-        <v>126</v>
-      </c>
-      <c r="D43">
-        <v>109.64293000000001</v>
-      </c>
-      <c r="E43">
-        <v>0.32357999999999998</v>
-      </c>
-      <c r="F43" t="s">
-        <v>103</v>
-      </c>
-      <c r="G43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H43" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>127</v>
-      </c>
-      <c r="B44" t="s">
-        <v>128</v>
-      </c>
-      <c r="C44" t="s">
-        <v>129</v>
-      </c>
-      <c r="D44">
-        <v>112.92764</v>
-      </c>
-      <c r="E44">
-        <v>0.83287</v>
-      </c>
-      <c r="F44" t="s">
-        <v>103</v>
-      </c>
-      <c r="G44" t="s">
-        <v>12</v>
-      </c>
-      <c r="H44" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>130</v>
-      </c>
-      <c r="B45" t="s">
-        <v>131</v>
-      </c>
-      <c r="C45" t="s">
-        <v>132</v>
-      </c>
-      <c r="D45">
-        <v>101.17953</v>
-      </c>
-      <c r="E45">
-        <v>1.26522</v>
-      </c>
-      <c r="F45" t="s">
-        <v>11</v>
-      </c>
-      <c r="G45" t="s">
-        <v>12</v>
-      </c>
-      <c r="H45" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>130</v>
-      </c>
-      <c r="B46" t="s">
-        <v>133</v>
-      </c>
-      <c r="C46" t="s">
-        <v>134</v>
-      </c>
-      <c r="D46">
-        <v>101.18324</v>
-      </c>
-      <c r="E46">
-        <v>1.26054</v>
-      </c>
-      <c r="F46" t="s">
-        <v>11</v>
-      </c>
-      <c r="G46" t="s">
-        <v>12</v>
-      </c>
-      <c r="H46" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>135</v>
-      </c>
-      <c r="B47" t="s">
-        <v>136</v>
-      </c>
-      <c r="C47" t="s">
-        <v>137</v>
-      </c>
-      <c r="D47">
-        <v>101.51934</v>
-      </c>
-      <c r="E47">
-        <v>-0.38468000000000002</v>
-      </c>
-      <c r="F47" t="s">
-        <v>11</v>
-      </c>
-      <c r="G47" t="s">
-        <v>12</v>
-      </c>
-      <c r="H47" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>135</v>
-      </c>
-      <c r="B48" t="s">
-        <v>138</v>
-      </c>
-      <c r="C48" t="s">
-        <v>139</v>
-      </c>
-      <c r="D48">
-        <v>101.55871999999999</v>
-      </c>
-      <c r="E48">
-        <v>-0.35905999999999999</v>
-      </c>
-      <c r="F48" t="s">
-        <v>11</v>
-      </c>
-      <c r="G48" t="s">
-        <v>12</v>
-      </c>
-      <c r="H48" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>140</v>
-      </c>
-      <c r="B49" t="s">
-        <v>141</v>
-      </c>
-      <c r="C49" t="s">
-        <v>142</v>
-      </c>
-      <c r="D49">
-        <v>99.656499999999994</v>
-      </c>
-      <c r="E49">
-        <v>2.9799500000000001</v>
-      </c>
-      <c r="F49" t="s">
-        <v>11</v>
-      </c>
-      <c r="G49" t="s">
-        <v>12</v>
-      </c>
-      <c r="H49" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>140</v>
-      </c>
-      <c r="B50" t="s">
-        <v>143</v>
-      </c>
-      <c r="C50" t="s">
-        <v>144</v>
+      <c r="C50">
+        <v>99.671440000000004</v>
       </c>
       <c r="D50">
-        <v>99.671440000000004</v>
-      </c>
-      <c r="E50">
         <v>2.9796100000000001</v>
       </c>
+      <c r="E50" t="s">
+        <v>9</v>
+      </c>
       <c r="F50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G50" t="s">
-        <v>12</v>
-      </c>
-      <c r="H50" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/template/Template_Insert_Ring.xlsx
+++ b/data/template/Template_Insert_Ring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JACOBS\SERVICE\API\data\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DCB7BB-805C-4A41-92F5-67A91426B352}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432D6638-D052-447C-9356-373F3970B69D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,28 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="112">
-  <si>
-    <t>Site ID</t>
-  </si>
-  <si>
-    <t>Site Name</t>
-  </si>
-  <si>
-    <t>Long</t>
-  </si>
-  <si>
-    <t>Lat</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Vendor</t>
-  </si>
-  <si>
-    <t>Program</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="104">
   <si>
     <t>04PBR0143</t>
   </si>
@@ -49,12 +28,6 @@
     <t>KAYUMASTAMPAN_HS</t>
   </si>
   <si>
-    <t>NSRO</t>
-  </si>
-  <si>
-    <t>TBG</t>
-  </si>
-  <si>
     <t>TX Expansion 2026</t>
   </si>
   <si>
@@ -94,18 +67,12 @@
     <t>KUTOHARJO_PAT_TB</t>
   </si>
   <si>
-    <t>CJRO</t>
-  </si>
-  <si>
     <t>16TAG0027</t>
   </si>
   <si>
     <t>PTULUNGAGU_CM</t>
   </si>
   <si>
-    <t>EJRO</t>
-  </si>
-  <si>
     <t>14PAT0108</t>
   </si>
   <si>
@@ -244,9 +211,6 @@
     <t>IN_TRANSMARTLAMPUNG_TB</t>
   </si>
   <si>
-    <t>SSRO</t>
-  </si>
-  <si>
     <t>09TJK0186</t>
   </si>
   <si>
@@ -265,9 +229,6 @@
     <t>INHUTANI_SAMBARATA_PL</t>
   </si>
   <si>
-    <t>KRO</t>
-  </si>
-  <si>
     <t>22SMR0050</t>
   </si>
   <si>
@@ -356,6 +317,21 @@
   </si>
   <si>
     <t>SIUMBUT_UMBUT2_MT</t>
+  </si>
+  <si>
+    <t>site_id</t>
+  </si>
+  <si>
+    <t>site_name</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>lat</t>
+  </si>
+  <si>
+    <t>program</t>
   </si>
 </sst>
 </file>
@@ -1196,38 +1172,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
       </c>
       <c r="C2">
         <v>101.42328999999999</v>
@@ -1236,21 +1206,15 @@
         <v>0.54040999999999995</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>101.42773</v>
@@ -1259,21 +1223,15 @@
         <v>0.53978999999999999</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>101.44167</v>
@@ -1282,21 +1240,15 @@
         <v>0.53056000000000003</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>100.363</v>
@@ -1305,21 +1257,15 @@
         <v>-0.92710000000000004</v>
       </c>
       <c r="E5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="F5" t="s">
+      <c r="B6" t="s">
         <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
       </c>
       <c r="C6">
         <v>100.35799</v>
@@ -1328,21 +1274,15 @@
         <v>-0.91257999999999995</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>100.35</v>
@@ -1351,21 +1291,15 @@
         <v>-0.91364999999999996</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C8">
         <v>111.04684</v>
@@ -1374,21 +1308,15 @@
         <v>-6.7325299999999997</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <v>111.84614000000001</v>
@@ -1397,21 +1325,15 @@
         <v>-8.1246899999999993</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>111.06310999999999</v>
@@ -1420,21 +1342,15 @@
         <v>-6.6002400000000003</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <v>111.06431000000001</v>
@@ -1443,21 +1359,15 @@
         <v>-6.5924199999999997</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <v>112.67862</v>
@@ -1466,21 +1376,15 @@
         <v>-7.4958600000000004</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C13">
         <v>112.70261000000001</v>
@@ -1489,21 +1393,15 @@
         <v>-7.5037599999999998</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C14">
         <v>101.41916999999999</v>
@@ -1512,21 +1410,15 @@
         <v>0.53244999999999998</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C15">
         <v>101.36835000000001</v>
@@ -1535,21 +1427,15 @@
         <v>0.49974000000000002</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C16">
         <v>109.65649999999999</v>
@@ -1558,21 +1444,15 @@
         <v>-7.6699200000000003</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>99.166569999999993</v>
@@ -1581,21 +1461,15 @@
         <v>3.3250099999999998</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C18">
         <v>99.170400000000001</v>
@@ -1604,21 +1478,15 @@
         <v>3.3297599999999998</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C19">
         <v>98.686920000000001</v>
@@ -1627,21 +1495,15 @@
         <v>3.5880800000000002</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C20">
         <v>98.609759999999994</v>
@@ -1650,21 +1512,15 @@
         <v>3.5494500000000002</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C21">
         <v>98.617609999999999</v>
@@ -1673,21 +1529,15 @@
         <v>3.5617700000000001</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C22">
         <v>98.620999999999995</v>
@@ -1696,21 +1546,15 @@
         <v>3.5648300000000002</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C23">
         <v>100.38639999999999</v>
@@ -1719,21 +1563,15 @@
         <v>-0.89912999999999998</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>101.37954000000001</v>
@@ -1742,21 +1580,15 @@
         <v>0.46812999999999999</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>101.41200000000001</v>
@@ -1765,21 +1597,15 @@
         <v>0.47427999999999998</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>104.46536</v>
@@ -1788,21 +1614,15 @@
         <v>0.92771999999999999</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>100.405</v>
@@ -1811,21 +1631,15 @@
         <v>-0.88815</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C28">
         <v>100.37808</v>
@@ -1834,21 +1648,15 @@
         <v>-0.93301999999999996</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C29">
         <v>100.45061</v>
@@ -1857,21 +1665,15 @@
         <v>-0.95757999999999999</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C30">
         <v>111.9761111</v>
@@ -1880,21 +1682,15 @@
         <v>-6.7945277800000001</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
-      </c>
-      <c r="F30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C31">
         <v>110.627</v>
@@ -1903,21 +1699,15 @@
         <v>-8.0922400000000003</v>
       </c>
       <c r="E31" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C32">
         <v>105.28211</v>
@@ -1926,21 +1716,15 @@
         <v>-5.3830600000000004</v>
       </c>
       <c r="E32" t="s">
-        <v>74</v>
-      </c>
-      <c r="F32" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C33">
         <v>105.27692</v>
@@ -1949,21 +1733,15 @@
         <v>-5.3914499999999999</v>
       </c>
       <c r="E33" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C34">
         <v>105.27185</v>
@@ -1972,21 +1750,15 @@
         <v>-5.3888999999999996</v>
       </c>
       <c r="E34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F34" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C35">
         <v>117.47207</v>
@@ -1995,21 +1767,15 @@
         <v>2.1488299999999998</v>
       </c>
       <c r="E35" t="s">
-        <v>81</v>
-      </c>
-      <c r="F35" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C36">
         <v>117.12284</v>
@@ -2018,21 +1784,15 @@
         <v>-0.50209000000000004</v>
       </c>
       <c r="E36" t="s">
-        <v>81</v>
-      </c>
-      <c r="F36" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C37">
         <v>117.14816999999999</v>
@@ -2041,21 +1801,15 @@
         <v>-0.47642000000000001</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
-      </c>
-      <c r="F37" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C38">
         <v>11721049</v>
@@ -2064,21 +1818,15 @@
         <v>-0.64832999999999996</v>
       </c>
       <c r="E38" t="s">
-        <v>81</v>
-      </c>
-      <c r="F38" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C39">
         <v>109.95220999999999</v>
@@ -2087,21 +1835,15 @@
         <v>-1.7906299999999999</v>
       </c>
       <c r="E39" t="s">
-        <v>81</v>
-      </c>
-      <c r="F39" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C40">
         <v>115.246</v>
@@ -2110,21 +1852,15 @@
         <v>-2.4285399999999999</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
-      </c>
-      <c r="F40" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C41">
         <v>111.43434000000001</v>
@@ -2133,21 +1869,15 @@
         <v>-2.1887400000000001</v>
       </c>
       <c r="E41" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>81</v>
       </c>
-      <c r="F41" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>94</v>
-      </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C42">
         <v>109.28449000000001</v>
@@ -2156,21 +1886,15 @@
         <v>0.34316999999999998</v>
       </c>
       <c r="E42" t="s">
-        <v>81</v>
-      </c>
-      <c r="F42" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C43">
         <v>109.64293000000001</v>
@@ -2179,21 +1903,15 @@
         <v>0.32357999999999998</v>
       </c>
       <c r="E43" t="s">
-        <v>81</v>
-      </c>
-      <c r="F43" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C44">
         <v>112.92764</v>
@@ -2202,21 +1920,15 @@
         <v>0.83287</v>
       </c>
       <c r="E44" t="s">
-        <v>81</v>
-      </c>
-      <c r="F44" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C45">
         <v>101.17953</v>
@@ -2225,21 +1937,15 @@
         <v>1.26522</v>
       </c>
       <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C46">
         <v>101.18324</v>
@@ -2248,21 +1954,15 @@
         <v>1.26054</v>
       </c>
       <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C47">
         <v>101.51934</v>
@@ -2271,21 +1971,15 @@
         <v>-0.38468000000000002</v>
       </c>
       <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C48">
         <v>101.55871999999999</v>
@@ -2294,21 +1988,15 @@
         <v>-0.35905999999999999</v>
       </c>
       <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C49">
         <v>99.656499999999994</v>
@@ -2317,21 +2005,15 @@
         <v>2.9799500000000001</v>
       </c>
       <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C50">
         <v>99.671440000000004</v>
@@ -2340,13 +2022,7 @@
         <v>2.9796100000000001</v>
       </c>
       <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
